--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.62159427934773</v>
+        <v>8.713509070394005</v>
       </c>
       <c r="D2" t="n">
-        <v>54.97829321348314</v>
+        <v>8.933972647191011</v>
       </c>
       <c r="E2" t="n">
-        <v>16.75365090525175</v>
+        <v>2.72246827210341</v>
       </c>
       <c r="F2" t="n">
-        <v>16.85998008452948</v>
+        <v>2.73974676373604</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.70595308631434</v>
+        <v>5.31471737652608</v>
       </c>
       <c r="D3" t="n">
-        <v>32.27299821720964</v>
+        <v>5.244362210296567</v>
       </c>
       <c r="E3" t="n">
-        <v>16.75365090525175</v>
+        <v>2.72246827210341</v>
       </c>
       <c r="F3" t="n">
-        <v>16.85998008452948</v>
+        <v>2.73974676373604</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.56661716168127</v>
+        <v>7.567075288773207</v>
       </c>
       <c r="D4" t="n">
-        <v>46.5400738478579</v>
+        <v>7.562762000276909</v>
       </c>
       <c r="E4" t="n">
-        <v>16.75365090525175</v>
+        <v>2.72246827210341</v>
       </c>
       <c r="F4" t="n">
-        <v>16.85998008452948</v>
+        <v>2.73974676373604</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.77400718011413</v>
+        <v>10.20077616676855</v>
       </c>
       <c r="D5" t="n">
-        <v>62.70012734646965</v>
+        <v>10.18877069380132</v>
       </c>
       <c r="E5" t="n">
-        <v>16.75365090525175</v>
+        <v>2.72246827210341</v>
       </c>
       <c r="F5" t="n">
-        <v>16.85998008452948</v>
+        <v>2.73974676373604</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.98785386281514</v>
+        <v>2.43552625270746</v>
       </c>
       <c r="D6" t="n">
-        <v>15.35754831825677</v>
+        <v>2.495601601716725</v>
       </c>
       <c r="E6" t="n">
-        <v>16.75365090525175</v>
+        <v>2.72246827210341</v>
       </c>
       <c r="F6" t="n">
-        <v>16.85998008452948</v>
+        <v>2.73974676373604</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
